--- a/research/traditional_assets/database/data/jamaica/jamaica_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_hospitals_healthcare_facilities.xlsx
@@ -587,23 +587,29 @@
           <t>Hospitals/Healthcare Facilities</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.308</v>
+      </c>
+      <c r="E2">
+        <v>-0.322</v>
+      </c>
       <c r="G2">
-        <v>-0.3612040133779264</v>
+        <v>-0.06415094339622641</v>
       </c>
       <c r="H2">
-        <v>-0.3612040133779264</v>
+        <v>-0.06415094339622641</v>
       </c>
       <c r="I2">
-        <v>-0.3032329988851728</v>
+        <v>-0.1424528301886792</v>
       </c>
       <c r="J2">
-        <v>-0.3032329988851728</v>
+        <v>-0.1424528301886792</v>
       </c>
       <c r="K2">
-        <v>0.281</v>
+        <v>0.15</v>
       </c>
       <c r="L2">
-        <v>0.3132664437012264</v>
+        <v>0.1415094339622641</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.126</v>
+        <v>0.016</v>
       </c>
       <c r="V2">
-        <v>0.04468085106382979</v>
+        <v>0.004678362573099415</v>
       </c>
       <c r="W2">
-        <v>0.1033088235294118</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="X2">
-        <v>0.1933815805889062</v>
+        <v>0.2293409880247848</v>
       </c>
       <c r="Y2">
-        <v>-0.09007275705949445</v>
+        <v>-0.1772576546914515</v>
       </c>
       <c r="Z2">
-        <v>0.09045986284792257</v>
+        <v>0.1025740274820979</v>
       </c>
       <c r="AA2">
-        <v>-0.02743041549011699</v>
+        <v>-0.01461196051867621</v>
       </c>
       <c r="AB2">
-        <v>0.102186999792327</v>
+        <v>0.1476137723059082</v>
       </c>
       <c r="AC2">
-        <v>-0.129617415282444</v>
+        <v>-0.1622257328245844</v>
       </c>
       <c r="AD2">
-        <v>5.87</v>
+        <v>5.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.87</v>
+        <v>5.27</v>
       </c>
       <c r="AG2">
-        <v>5.744</v>
+        <v>5.254</v>
       </c>
       <c r="AH2">
-        <v>0.6754890678941312</v>
+        <v>0.6064441887226697</v>
       </c>
       <c r="AI2">
-        <v>0.5611854684512428</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="AJ2">
-        <v>0.6707146193367585</v>
+        <v>0.60571823841365</v>
       </c>
       <c r="AK2">
-        <v>0.555835107412425</v>
+        <v>0.5337261275904104</v>
       </c>
       <c r="AL2">
-        <v>0.258</v>
+        <v>0.279</v>
       </c>
       <c r="AM2">
-        <v>0.256</v>
+        <v>0.275</v>
       </c>
       <c r="AN2">
-        <v>-33.54285714285714</v>
+        <v>-89.32203389830508</v>
       </c>
       <c r="AO2">
-        <v>-1.054263565891473</v>
+        <v>-0.5412186379928314</v>
       </c>
       <c r="AP2">
-        <v>-32.82285714285715</v>
+        <v>-89.05084745762711</v>
       </c>
       <c r="AQ2">
-        <v>-1.0625</v>
+        <v>-0.5490909090909091</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +718,29 @@
           <t>Hospitals/Healthcare Facilities</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.308</v>
+      </c>
+      <c r="E3">
+        <v>-0.322</v>
+      </c>
       <c r="G3">
-        <v>-0.3612040133779264</v>
+        <v>-0.06415094339622641</v>
       </c>
       <c r="H3">
-        <v>-0.3612040133779264</v>
+        <v>-0.06415094339622641</v>
       </c>
       <c r="I3">
-        <v>-0.3032329988851728</v>
+        <v>-0.1424528301886792</v>
       </c>
       <c r="J3">
-        <v>-0.3032329988851728</v>
+        <v>-0.1424528301886792</v>
       </c>
       <c r="K3">
-        <v>0.281</v>
+        <v>0.15</v>
       </c>
       <c r="L3">
-        <v>0.3132664437012264</v>
+        <v>0.1415094339622641</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.126</v>
+        <v>0.016</v>
       </c>
       <c r="V3">
-        <v>0.04468085106382979</v>
+        <v>0.004678362573099415</v>
       </c>
       <c r="W3">
-        <v>0.1033088235294118</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="X3">
-        <v>0.1933815805889062</v>
+        <v>0.2293409880247848</v>
       </c>
       <c r="Y3">
-        <v>-0.09007275705949445</v>
+        <v>-0.1772576546914515</v>
       </c>
       <c r="Z3">
-        <v>0.09045986284792257</v>
+        <v>0.1025740274820979</v>
       </c>
       <c r="AA3">
-        <v>-0.02743041549011699</v>
+        <v>-0.01461196051867621</v>
       </c>
       <c r="AB3">
-        <v>0.102186999792327</v>
+        <v>0.1476137723059082</v>
       </c>
       <c r="AC3">
-        <v>-0.129617415282444</v>
+        <v>-0.1622257328245844</v>
       </c>
       <c r="AD3">
-        <v>5.87</v>
+        <v>5.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.87</v>
+        <v>5.27</v>
       </c>
       <c r="AG3">
-        <v>5.744</v>
+        <v>5.254</v>
       </c>
       <c r="AH3">
-        <v>0.6754890678941312</v>
+        <v>0.6064441887226697</v>
       </c>
       <c r="AI3">
-        <v>0.5611854684512428</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="AJ3">
-        <v>0.6707146193367585</v>
+        <v>0.60571823841365</v>
       </c>
       <c r="AK3">
-        <v>0.555835107412425</v>
+        <v>0.5337261275904104</v>
       </c>
       <c r="AL3">
-        <v>0.258</v>
+        <v>0.279</v>
       </c>
       <c r="AM3">
-        <v>0.256</v>
+        <v>0.275</v>
       </c>
       <c r="AN3">
-        <v>-33.54285714285714</v>
+        <v>-89.32203389830508</v>
       </c>
       <c r="AO3">
-        <v>-1.054263565891473</v>
+        <v>-0.5412186379928314</v>
       </c>
       <c r="AP3">
-        <v>-32.82285714285715</v>
+        <v>-89.05084745762711</v>
       </c>
       <c r="AQ3">
-        <v>-1.0625</v>
+        <v>-0.5490909090909091</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_hospitals_healthcare_facilities.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.308</v>
-      </c>
-      <c r="E2">
-        <v>-0.322</v>
+        <v>0.203</v>
       </c>
       <c r="G2">
-        <v>-0.06415094339622641</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="H2">
-        <v>-0.06415094339622641</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="I2">
-        <v>-0.1424528301886792</v>
+        <v>-0.1683823529411765</v>
       </c>
       <c r="J2">
-        <v>-0.1424528301886792</v>
+        <v>-0.1683823529411765</v>
       </c>
       <c r="K2">
-        <v>0.15</v>
+        <v>-0.048</v>
       </c>
       <c r="L2">
-        <v>0.1415094339622641</v>
+        <v>-0.03529411764705882</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="V2">
-        <v>0.004678362573099415</v>
+        <v>0.006204379562043796</v>
       </c>
       <c r="W2">
-        <v>0.05208333333333334</v>
+        <v>-0.0163265306122449</v>
       </c>
       <c r="X2">
-        <v>0.2293409880247848</v>
+        <v>0.1896414137523193</v>
       </c>
       <c r="Y2">
-        <v>-0.1772576546914515</v>
+        <v>-0.2059679443645642</v>
       </c>
       <c r="Z2">
-        <v>0.1025740274820979</v>
+        <v>0.1381552214546932</v>
       </c>
       <c r="AA2">
-        <v>-0.01461196051867621</v>
+        <v>-0.02326290125965055</v>
       </c>
       <c r="AB2">
-        <v>0.1476137723059082</v>
+        <v>0.1164687968892728</v>
       </c>
       <c r="AC2">
-        <v>-0.1622257328245844</v>
+        <v>-0.1397316981489234</v>
       </c>
       <c r="AD2">
-        <v>5.27</v>
+        <v>5.07</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.27</v>
+        <v>5.07</v>
       </c>
       <c r="AG2">
-        <v>5.254</v>
+        <v>5.053</v>
       </c>
       <c r="AH2">
-        <v>0.6064441887226697</v>
+        <v>0.6491677336747759</v>
       </c>
       <c r="AI2">
-        <v>0.5344827586206896</v>
+        <v>0.5342465753424658</v>
       </c>
       <c r="AJ2">
-        <v>0.60571823841365</v>
+        <v>0.6484024124214038</v>
       </c>
       <c r="AK2">
-        <v>0.5337261275904104</v>
+        <v>0.5334107463316795</v>
       </c>
       <c r="AL2">
-        <v>0.279</v>
+        <v>0.224</v>
       </c>
       <c r="AM2">
-        <v>0.275</v>
-      </c>
-      <c r="AN2">
-        <v>-89.32203389830508</v>
+        <v>0.223</v>
       </c>
       <c r="AO2">
-        <v>-0.5412186379928314</v>
-      </c>
-      <c r="AP2">
-        <v>-89.05084745762711</v>
+        <v>-1.022321428571429</v>
       </c>
       <c r="AQ2">
-        <v>-0.5490909090909091</v>
+        <v>-1.026905829596413</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.308</v>
-      </c>
-      <c r="E3">
-        <v>-0.322</v>
+        <v>0.203</v>
       </c>
       <c r="G3">
-        <v>-0.06415094339622641</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="H3">
-        <v>-0.06415094339622641</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="I3">
-        <v>-0.1424528301886792</v>
+        <v>-0.1683823529411765</v>
       </c>
       <c r="J3">
-        <v>-0.1424528301886792</v>
+        <v>-0.1683823529411765</v>
       </c>
       <c r="K3">
-        <v>0.15</v>
+        <v>-0.048</v>
       </c>
       <c r="L3">
-        <v>0.1415094339622641</v>
+        <v>-0.03529411764705882</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +746,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="V3">
-        <v>0.004678362573099415</v>
+        <v>0.006204379562043796</v>
       </c>
       <c r="W3">
-        <v>0.05208333333333334</v>
+        <v>-0.0163265306122449</v>
       </c>
       <c r="X3">
-        <v>0.2293409880247848</v>
+        <v>0.1896414137523193</v>
       </c>
       <c r="Y3">
-        <v>-0.1772576546914515</v>
+        <v>-0.2059679443645642</v>
       </c>
       <c r="Z3">
-        <v>0.1025740274820979</v>
+        <v>0.1381552214546932</v>
       </c>
       <c r="AA3">
-        <v>-0.01461196051867621</v>
+        <v>-0.02326290125965055</v>
       </c>
       <c r="AB3">
-        <v>0.1476137723059082</v>
+        <v>0.1164687968892728</v>
       </c>
       <c r="AC3">
-        <v>-0.1622257328245844</v>
+        <v>-0.1397316981489234</v>
       </c>
       <c r="AD3">
-        <v>5.27</v>
+        <v>5.07</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.27</v>
+        <v>5.07</v>
       </c>
       <c r="AG3">
-        <v>5.254</v>
+        <v>5.053</v>
       </c>
       <c r="AH3">
-        <v>0.6064441887226697</v>
+        <v>0.6491677336747759</v>
       </c>
       <c r="AI3">
-        <v>0.5344827586206896</v>
+        <v>0.5342465753424658</v>
       </c>
       <c r="AJ3">
-        <v>0.60571823841365</v>
+        <v>0.6484024124214038</v>
       </c>
       <c r="AK3">
-        <v>0.5337261275904104</v>
+        <v>0.5334107463316795</v>
       </c>
       <c r="AL3">
-        <v>0.279</v>
+        <v>0.224</v>
       </c>
       <c r="AM3">
-        <v>0.275</v>
-      </c>
-      <c r="AN3">
-        <v>-89.32203389830508</v>
+        <v>0.223</v>
       </c>
       <c r="AO3">
-        <v>-0.5412186379928314</v>
-      </c>
-      <c r="AP3">
-        <v>-89.05084745762711</v>
+        <v>-1.022321428571429</v>
       </c>
       <c r="AQ3">
-        <v>-0.5490909090909091</v>
+        <v>-1.026905829596413</v>
       </c>
     </row>
   </sheetData>
